--- a/employee_surveys/028_employee_work_life_balance_evaluation_form--employee_surveys.xlsx
+++ b/employee_surveys/028_employee_work_life_balance_evaluation_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,10 +440,10 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_evaluation_form</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Employee Work Life Balance Evaluation Form</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,15 +543,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_evaluation_form</t>
+          <t>work_life_balance_perception</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>On a scale of 1-5, how would you rate your perception of your work-life balance?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please rate your perception of your work-life balance.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +570,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_evaluation_form</t>
+          <t>work_life_balance_description</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Description of your work-life balance</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please describe your work-life balance in 100 words or less.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +592,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
+          <t>work_hours</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How many hours do you work per week?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please enter the number of hours you work per week.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +619,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
+          <t>work_life_balance_flexibility</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Do you feel you have sufficient flexibility in your work schedule?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +646,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
+          <t>communication_with_manager</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How would you rate the communication with your manager about your work-life balance?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select a date in the format YYYY-MM-DD.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +673,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
+          <t>support_from_manager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Has your manager supported you in achieving a better work-life balance?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select one of the options.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +700,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
+          <t>self_care_activities</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What self-care activities do you regularly engage in to maintain your well-being?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +732,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
+          <t>wellness_plan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you have a personal wellness plan in place?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select one of the options.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +754,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_evaluation_form</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Any additional feedback or comments?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide any additional feedback or comments you have about your work-life balance.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +786,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Do you have any suggestions for improving our work-life balance policies?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide any suggestions you may have.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,17 +808,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form</t>
+          <t>Do you have any contact information you'd like to provide?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,12 +839,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,102 +867,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form_choices</t>
+          <t>work_life_balance_flexibility_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category1'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'category1'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form_choices</t>
+          <t>work_life_balance_flexibility_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category2'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'category2'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form_choices</t>
+          <t>work_life_balance_flexibility_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'category3'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'category3'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form_choices</t>
+          <t>self_care_activities_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option1'}</t>
+          <t>yoga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'option1'}</t>
+          <t>yoga</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form_choices</t>
+          <t>self_care_activities_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option2'}</t>
+          <t>meditation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'option2'}</t>
+          <t>meditation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>employee_work_life_balance_form_choices</t>
+          <t>self_care_activities_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option3'}</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'option3'}</t>
+          <t>exercise</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>self_care_activities_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hobbies</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>hobbies</t>
         </is>
       </c>
     </row>
